--- a/docs/downloads/05/tbl_lighting_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_lighting_marovoay_tous.xlsx
@@ -490,12 +490,6 @@
           <t>Marovoay - Bepako</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -544,12 +538,6 @@
           <t>Bois De Chauffe</t>
         </is>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -629,12 +617,6 @@
           <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -768,12 +750,6 @@
           <t>Marovoay - Maroala</t>
         </is>
       </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -786,12 +762,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-      <c r="D25">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -888,12 +858,6 @@
         <is>
           <t>Marovoay - Tous</t>
         </is>
-      </c>
-      <c r="C31">
-        <v>4</v>
-      </c>
-      <c r="D31">
-        <v>0.5</v>
       </c>
     </row>
     <row r="32">

--- a/docs/downloads/05/tbl_lighting_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_lighting_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,7 +391,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>4.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -409,7 +409,7 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>6.9</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="4">
@@ -420,14 +420,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
+          <t>Piles</t>
         </is>
       </c>
       <c r="C4">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>16.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -438,14 +438,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Piles</t>
+          <t>Pétrole Lampant</t>
         </is>
       </c>
       <c r="C5">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D5">
-        <v>21.6</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="6">
@@ -456,32 +456,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pétrole Lampant</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C6">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="D6">
-        <v>32.9</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Solaire</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>41</v>
-      </c>
-      <c r="D7">
-        <v>17.7</v>
+          <t>Marovoay - Bepako</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -490,6 +479,17 @@
           <t>Marovoay - Bepako</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Autres</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <v>9.800000000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -499,14 +499,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Batteries</t>
         </is>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>5.3</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="10">
@@ -517,14 +517,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Batteries</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>22</v>
-      </c>
-      <c r="D10">
-        <v>9.699999999999999</v>
+          <t>Bois De Chauffe</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -535,8 +529,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bois De Chauffe</t>
-        </is>
+          <t>Piles</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>32</v>
+      </c>
+      <c r="D11">
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -547,14 +547,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
+          <t>Pétrole Lampant</t>
         </is>
       </c>
       <c r="C12">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="D12">
-        <v>21.2</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="13">
@@ -565,50 +565,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Piles</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C13">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D13">
-        <v>14.2</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Pétrole Lampant</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>66</v>
-      </c>
-      <c r="D14">
-        <v>29.2</v>
+          <t>Marovoay - Madiromiongana</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Solaire</t>
+          <t>Autres</t>
         </is>
       </c>
       <c r="C15">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>19.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="16">
@@ -617,6 +606,17 @@
           <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Batteries</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>12</v>
+      </c>
+      <c r="D16">
+        <v>8.800000000000001</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -626,14 +626,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Bois De Chauffe</t>
         </is>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="18">
@@ -644,14 +644,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Batteries</t>
+          <t>Piles</t>
         </is>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D18">
-        <v>5.9</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="19">
@@ -662,14 +662,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bois De Chauffe</t>
+          <t>Pétrole Lampant</t>
         </is>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="D19">
-        <v>2.5</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="20">
@@ -680,68 +680,51 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C20">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D20">
-        <v>12.3</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Piles</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>34</v>
-      </c>
-      <c r="D21">
-        <v>16.7</v>
+          <t>Marovoay - Maroala</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pétrole Lampant</t>
-        </is>
-      </c>
-      <c r="C22">
-        <v>97</v>
-      </c>
-      <c r="D22">
-        <v>47.8</v>
+          <t>Autres</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Solaire</t>
+          <t>Batteries</t>
         </is>
       </c>
       <c r="C23">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D23">
-        <v>10.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="24">
@@ -750,6 +733,17 @@
           <t>Marovoay - Maroala</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Piles</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>35</v>
+      </c>
+      <c r="D24">
+        <v>30.2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -759,8 +753,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
+          <t>Pétrole Lampant</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>44</v>
+      </c>
+      <c r="D25">
+        <v>37.9</v>
       </c>
     </row>
     <row r="26">
@@ -771,86 +771,75 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Batteries</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C26">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="D26">
-        <v>7.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Panneau Solaire En Marche ?</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>52</v>
-      </c>
-      <c r="D27">
-        <v>25.4</v>
+          <t>Marovoay - Tous</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Piles</t>
+          <t>Autres</t>
         </is>
       </c>
       <c r="C28">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D28">
-        <v>17.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pétrole Lampant</t>
+          <t>Batteries</t>
         </is>
       </c>
       <c r="C29">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D29">
-        <v>21.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Solaire</t>
+          <t>Bois De Chauffe</t>
         </is>
       </c>
       <c r="C30">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>26.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="31">
@@ -859,6 +848,17 @@
           <t>Marovoay - Tous</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Piles</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>151</v>
+      </c>
+      <c r="D31">
+        <v>29.1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -868,14 +868,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Pétrole Lampant</t>
         </is>
       </c>
       <c r="C32">
-        <v>31</v>
+        <v>283</v>
       </c>
       <c r="D32">
-        <v>3.6</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="33">
@@ -886,104 +886,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Batteries</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C33">
-        <v>65</v>
+        <v>162</v>
       </c>
       <c r="D33">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Bois De Chauffe</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>6</v>
-      </c>
-      <c r="D34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Panneau Solaire En Marche ?</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>163</v>
-      </c>
-      <c r="D35">
-        <v>18.8</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Piles</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>151</v>
-      </c>
-      <c r="D36">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Pétrole Lampant</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>283</v>
-      </c>
-      <c r="D37">
-        <v>32.7</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Solaire</t>
-        </is>
-      </c>
-      <c r="C38">
-        <v>162</v>
-      </c>
-      <c r="D38">
-        <v>18.7</v>
+        <v>31.2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/05/tbl_lighting_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_lighting_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -469,14 +469,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -494,7 +494,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -542,7 +542,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -560,7 +560,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -578,14 +578,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -603,7 +603,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -693,14 +693,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -730,7 +730,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -748,7 +748,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -784,14 +784,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -809,7 +809,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -881,7 +881,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
